--- a/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_0_9.xlsx
+++ b/model/Output_Budget/1. Baseline/Grid Search/Output Files/100000/Output_0_9.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>320071.4256334111</v>
+        <v>317362.5407815019</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2995127.424547405</v>
+        <v>2995243.613506387</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20355556.36745724</v>
+        <v>20355670.24425593</v>
       </c>
     </row>
     <row r="9">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4812396.678818937</v>
+        <v>4812058.022867889</v>
       </c>
     </row>
     <row r="11">
@@ -1123,16 +1123,16 @@
         <v>0</v>
       </c>
       <c r="C8" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="E8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="9">
@@ -1199,13 +1199,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>22.56635248423083</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1217,13 +1217,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22.15420867374214</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1293,16 +1293,16 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H10" t="n">
-        <v>23.55275130756107</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K10" t="n">
         <v>22.26949182588285</v>
@@ -1320,7 +1320,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1402,22 +1402,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S11" t="n">
-        <v>22.90079999999999</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U11" t="n">
-        <v>26</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -1457,7 +1457,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="J12" t="n">
         <v>0.7465913262578567</v>
@@ -1487,16 +1487,16 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>22.15420867374214</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -1505,7 +1505,7 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
     </row>
     <row r="13">
@@ -1530,16 +1530,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H13" t="n">
-        <v>23.55275130756091</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K13" t="n">
         <v>22.26949182588285</v>
@@ -1557,7 +1557,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1639,19 +1639,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="S14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="T14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="U14" t="n">
-        <v>22.90079999999999</v>
+        <v>12.57565326968602</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1685,19 +1685,19 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>21.81976115797297</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="H15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1721,13 +1721,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>22.90079999999999</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1767,16 +1767,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2741920426674241</v>
+        <v>0.2968606583479769</v>
       </c>
       <c r="H16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="J16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="K16" t="n">
         <v>22.26949182588285</v>
@@ -1843,19 +1843,19 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>24.66239999999999</v>
+        <v>12.35200489467393</v>
       </c>
       <c r="G17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>11.94928935461252</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -1916,13 +1916,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>24.66239999999999</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -1958,16 +1958,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>24.30129424928645</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1989,7 +1989,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22.02246762618611</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -2037,25 +2037,25 @@
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>22.44875936050941</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="V19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -2068,22 +2068,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>212.2853856434421</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>202.2821007854552</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2131,13 +2131,13 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
     </row>
     <row r="21">
@@ -2150,19 +2150,19 @@
         <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D21" t="n">
-        <v>122.6204988630871</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -2171,7 +2171,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -2195,22 +2195,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S21" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.55522121023865</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2277,16 +2277,16 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
         <v>133.186967585368</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -2305,22 +2305,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>212.2728</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -2353,16 +2353,16 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>21.18375537072436</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2384,31 +2384,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>147.4450655646388</v>
+        <v>92.72704515543269</v>
       </c>
       <c r="E24" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2450,10 +2450,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>85.25827556447292</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -2526,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>212.2728</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="C26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -2587,13 +2587,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>52.42556848774752</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="Y26" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2621,25 +2621,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F27" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>112.8975621594047</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2669,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>55.28127355395444</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T27" t="n">
         <v>0</v>
@@ -2681,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>232.8005871494253</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -2751,7 +2751,7 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2782,22 +2782,22 @@
         <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>202.2821007854552</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="F29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>241</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>241</v>
+        <v>84.41978777916125</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2827,10 +2827,10 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>209.0200695862453</v>
       </c>
       <c r="T29" t="n">
         <v>0</v>
@@ -2861,13 +2861,13 @@
         <v>0</v>
       </c>
       <c r="C30" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>76.47811836767261</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>29.79900896488263</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -2915,19 +2915,19 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V30" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y30" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2994,13 +2994,13 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
         <v>0</v>
@@ -3025,10 +3025,10 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F32" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3070,13 +3070,13 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>189.372</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
     </row>
     <row r="33">
@@ -3098,19 +3098,19 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>157.6450804554009</v>
       </c>
       <c r="F33" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>137.3435171632106</v>
+        <v>91.01404827120737</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -3143,16 +3143,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>74.16062543505004</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -3216,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>44.30348359856713</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -3256,19 +3256,19 @@
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3307,16 +3307,16 @@
         <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>189.372</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="W35" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>0</v>
@@ -3332,13 +3332,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3347,16 +3347,16 @@
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>18.03586205537343</v>
       </c>
       <c r="I36" t="n">
-        <v>3.822158104232112</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -3383,22 +3383,22 @@
         <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T36" t="n">
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X36" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -3432,13 +3432,13 @@
         <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>110.9174757594851</v>
+        <v>0</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>22.26949182588285</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>44.30348359856706</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3490,19 +3490,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0</v>
+        <v>189.7190331592112</v>
       </c>
       <c r="C38" t="n">
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -3511,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>189.3719999999999</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3547,13 +3547,13 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="X38" t="n">
         <v>0</v>
@@ -3572,13 +3572,13 @@
         <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>108.5991582026559</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>157.6450804554009</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3617,19 +3617,19 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U39" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>148.5012945739651</v>
       </c>
       <c r="W39" t="n">
         <v>0</v>
@@ -3638,7 +3638,7 @@
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3651,13 +3651,13 @@
         <v>0</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>133.186967585368</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
       </c>
       <c r="E40" t="n">
-        <v>133.186967585368</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
         <v>0</v>
@@ -3727,10 +3727,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="C41" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3739,13 +3739,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>187.6104</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3775,16 +3775,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>149.8691179411497</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>38.11497345300587</v>
       </c>
       <c r="T41" t="n">
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>213</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3806,13 +3806,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>166.5331836498673</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -3824,7 +3824,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3854,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>81.25479045854401</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -3863,19 +3863,19 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>129.1590763363318</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>205.6826957773044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -4763,76 +4763,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="C8" t="n">
-        <v>80.86787878787879</v>
+        <v>50.72300074896609</v>
       </c>
       <c r="D8" t="n">
-        <v>54.60525252525252</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="E8" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J8" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K8" t="n">
-        <v>26.78000000000001</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L8" t="n">
-        <v>26.78000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M8" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N8" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T8" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U8" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="V8" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W8" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X8" t="n">
-        <v>104</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y8" t="n">
-        <v>104</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="9">
@@ -4842,76 +4842,76 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51.47474747474747</v>
+        <v>53.80778732512771</v>
       </c>
       <c r="C9" t="n">
-        <v>51.47474747474747</v>
+        <v>27.92870531034908</v>
       </c>
       <c r="D9" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E9" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F9" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G9" t="n">
-        <v>51.47474747474747</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H9" t="n">
-        <v>29.09675891541198</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I9" t="n">
-        <v>2.834132652785714</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K9" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L9" t="n">
-        <v>27.82</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M9" t="n">
-        <v>27.82</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N9" t="n">
-        <v>27.82</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O9" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P9" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q9" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V9" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W9" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X9" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y9" t="n">
-        <v>77.73737373737373</v>
+        <v>76.6020827637447</v>
       </c>
     </row>
     <row r="10">
@@ -4921,76 +4921,76 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H10" t="n">
-        <v>77.09968871301299</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I10" t="n">
-        <v>50.83706245038672</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J10" t="n">
-        <v>24.57443618776046</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K10" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L10" t="n">
-        <v>27.82000000000018</v>
+        <v>27.413711578255</v>
       </c>
       <c r="M10" t="n">
-        <v>53.56000000000017</v>
+        <v>52.77779986093952</v>
       </c>
       <c r="N10" t="n">
-        <v>79.30000000000017</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O10" t="n">
-        <v>103.6392766348994</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y10" t="n">
-        <v>100.8903465994383</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="11">
@@ -5000,76 +5000,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K11" t="n">
-        <v>26.78000000000001</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L11" t="n">
-        <v>26.78000000000001</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M11" t="n">
-        <v>26.78000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N11" t="n">
-        <v>52.52000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O11" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P11" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q11" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R11" t="n">
-        <v>104</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S11" t="n">
-        <v>80.86787878787879</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T11" t="n">
-        <v>54.60525252525252</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U11" t="n">
-        <v>28.34262626262626</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="12">
@@ -5079,76 +5079,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="C12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="D12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="E12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="F12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="G12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="H12" t="n">
-        <v>2.834132652785714</v>
+        <v>24.84391873418747</v>
       </c>
       <c r="I12" t="n">
-        <v>2.834132652785714</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J12" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K12" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L12" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P12" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="Q12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R12" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S12" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T12" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U12" t="n">
-        <v>25.2121212121212</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V12" t="n">
-        <v>2.834132652785714</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="W12" t="n">
-        <v>2.834132652785714</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="X12" t="n">
-        <v>2.834132652785714</v>
+        <v>76.6020827637447</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.834132652785714</v>
+        <v>50.72300074896609</v>
       </c>
     </row>
     <row r="13">
@@ -5158,76 +5158,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H13" t="n">
-        <v>77.46041207811371</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I13" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J13" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K13" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L13" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M13" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N13" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O13" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y13" t="n">
-        <v>101.2510699645389</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="14">
@@ -5237,76 +5237,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="C14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="D14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="E14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="F14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="G14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="H14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="I14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="J14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K14" t="n">
-        <v>27.82</v>
+        <v>26.38889993046976</v>
       </c>
       <c r="L14" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M14" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N14" t="n">
-        <v>53.56</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O14" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="P14" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q14" t="n">
-        <v>104</v>
+        <v>92.38954941029624</v>
       </c>
       <c r="R14" t="n">
-        <v>77.73737373737373</v>
+        <v>66.51046739551762</v>
       </c>
       <c r="S14" t="n">
-        <v>51.47474747474747</v>
+        <v>40.631385380739</v>
       </c>
       <c r="T14" t="n">
-        <v>25.2121212121212</v>
+        <v>14.75230336596039</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="V14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="W14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="X14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
     </row>
     <row r="15">
@@ -5316,76 +5316,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F15" t="n">
-        <v>28.34262626262626</v>
+        <v>80.44100199269204</v>
       </c>
       <c r="G15" t="n">
-        <v>28.34262626262626</v>
+        <v>54.56191997791342</v>
       </c>
       <c r="H15" t="n">
-        <v>2.08</v>
+        <v>28.6828379631348</v>
       </c>
       <c r="I15" t="n">
-        <v>2.08</v>
+        <v>2.80375594835618</v>
       </c>
       <c r="J15" t="n">
-        <v>2.08</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="K15" t="n">
-        <v>27.82</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="L15" t="n">
-        <v>53.56</v>
+        <v>51.75298821315428</v>
       </c>
       <c r="M15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="N15" t="n">
-        <v>78.26000000000001</v>
+        <v>77.1170764958388</v>
       </c>
       <c r="O15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P15" t="n">
-        <v>78.26000000000001</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q15" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R15" t="n">
-        <v>77.73737373737373</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S15" t="n">
-        <v>51.47474747474747</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y15" t="n">
-        <v>28.34262626262626</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="16">
@@ -5395,76 +5395,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="C16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="D16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="E16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="G16" t="n">
-        <v>103.72303834074</v>
+        <v>102.1813055276668</v>
       </c>
       <c r="H16" t="n">
-        <v>77.46041207811371</v>
+        <v>76.30222351288816</v>
       </c>
       <c r="I16" t="n">
-        <v>51.19778581548745</v>
+        <v>50.42314149810954</v>
       </c>
       <c r="J16" t="n">
-        <v>24.93515955286119</v>
+        <v>24.54405948333093</v>
       </c>
       <c r="K16" t="n">
-        <v>2.44072336510073</v>
+        <v>2.049623295570466</v>
       </c>
       <c r="L16" t="n">
-        <v>28.18072336510073</v>
+        <v>27.41371157825499</v>
       </c>
       <c r="M16" t="n">
-        <v>53.92072336510073</v>
+        <v>52.77779986093951</v>
       </c>
       <c r="N16" t="n">
-        <v>79.66072336510072</v>
+        <v>78.14188814362404</v>
       </c>
       <c r="O16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="P16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Q16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="R16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="S16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="T16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="U16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="V16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="W16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="X16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
       <c r="Y16" t="n">
-        <v>104</v>
+        <v>102.4811647785233</v>
       </c>
     </row>
     <row r="17">
@@ -5474,76 +5474,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="C17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="E17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="F17" t="n">
-        <v>87.08848484848485</v>
+        <v>97.8833284203818</v>
       </c>
       <c r="G17" t="n">
-        <v>58.80565656565657</v>
+        <v>70.01461603622408</v>
       </c>
       <c r="H17" t="n">
-        <v>30.52282828282829</v>
+        <v>42.14590365206637</v>
       </c>
       <c r="I17" t="n">
-        <v>2.24</v>
+        <v>14.27719126790864</v>
       </c>
       <c r="J17" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K17" t="n">
-        <v>29.96</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L17" t="n">
-        <v>57.68</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M17" t="n">
-        <v>84.28</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N17" t="n">
-        <v>84.28</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O17" t="n">
-        <v>84.28</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="P17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="S17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="T17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="U17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="V17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="W17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="X17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Y17" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
     </row>
     <row r="18">
@@ -5553,76 +5553,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D18" t="n">
-        <v>55.43434343434343</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E18" t="n">
-        <v>27.15151515151514</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K18" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L18" t="n">
-        <v>2.24</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M18" t="n">
-        <v>2.24</v>
+        <v>55.73185102583861</v>
       </c>
       <c r="N18" t="n">
-        <v>28.84</v>
+        <v>83.04597603355158</v>
       </c>
       <c r="O18" t="n">
-        <v>56.56</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="P18" t="n">
-        <v>84.28</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="Q18" t="n">
-        <v>112</v>
+        <v>110.3601010412646</v>
       </c>
       <c r="R18" t="n">
-        <v>112</v>
+        <v>82.49138865710684</v>
       </c>
       <c r="S18" t="n">
-        <v>112</v>
+        <v>54.62267627294912</v>
       </c>
       <c r="T18" t="n">
-        <v>112</v>
+        <v>26.7539638887914</v>
       </c>
       <c r="U18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="V18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="W18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="X18" t="n">
-        <v>112</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y18" t="n">
-        <v>83.71717171717171</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="19">
@@ -5632,76 +5632,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="C19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="D19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="F19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="G19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="H19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="I19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="J19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="K19" t="n">
-        <v>2.24</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="L19" t="n">
-        <v>29.55412500771298</v>
+        <v>29.52132702853827</v>
       </c>
       <c r="M19" t="n">
-        <v>57.27412500771297</v>
+        <v>56.83545203625125</v>
       </c>
       <c r="N19" t="n">
-        <v>84.99412500771297</v>
+        <v>84.14957704396423</v>
       </c>
       <c r="O19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="P19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="Q19" t="n">
-        <v>109.3334016426122</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="R19" t="n">
-        <v>81.05057335978395</v>
+        <v>108.4888536788635</v>
       </c>
       <c r="S19" t="n">
-        <v>81.05057335978395</v>
+        <v>85.81333917329844</v>
       </c>
       <c r="T19" t="n">
-        <v>81.05057335978395</v>
+        <v>57.94462678914073</v>
       </c>
       <c r="U19" t="n">
-        <v>81.05057335978395</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="V19" t="n">
-        <v>52.76774507695567</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="W19" t="n">
-        <v>24.48491679412739</v>
+        <v>30.07591440498301</v>
       </c>
       <c r="X19" t="n">
-        <v>24.48491679412739</v>
+        <v>2.207202020825291</v>
       </c>
       <c r="Y19" t="n">
-        <v>24.48491679412739</v>
+        <v>2.207202020825291</v>
       </c>
     </row>
     <row r="20">
@@ -5711,76 +5711,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>506.1486868686869</v>
+        <v>477.1596022224361</v>
       </c>
       <c r="C20" t="n">
-        <v>506.1486868686869</v>
+        <v>233.7108255783361</v>
       </c>
       <c r="D20" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E20" t="n">
-        <v>506.1486868686869</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F20" t="n">
-        <v>262.7143434343434</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J20" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K20" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L20" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M20" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N20" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O20" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P20" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S20" t="n">
-        <v>953.9083846317729</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T20" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U20" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="V20" t="n">
-        <v>749.5830303030303</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="W20" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="X20" t="n">
-        <v>506.1486868686869</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Y20" t="n">
-        <v>506.1486868686869</v>
+        <v>720.6083788665362</v>
       </c>
     </row>
     <row r="21">
@@ -5790,76 +5790,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>588.3960608094349</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="C21" t="n">
-        <v>588.3960608094349</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D21" t="n">
-        <v>464.5369710487408</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E21" t="n">
-        <v>305.2995160432853</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F21" t="n">
-        <v>158.7649580701702</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I21" t="n">
-        <v>20.03413265278571</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J21" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K21" t="n">
-        <v>74.21341651829999</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L21" t="n">
-        <v>304.1765223866491</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="M21" t="n">
-        <v>542.7665223866492</v>
+        <v>234.810827406191</v>
       </c>
       <c r="N21" t="n">
-        <v>542.7665223866492</v>
+        <v>473.4149733950735</v>
       </c>
       <c r="O21" t="n">
-        <v>781.3565223866492</v>
+        <v>712.019119383956</v>
       </c>
       <c r="P21" t="n">
-        <v>964</v>
+        <v>894.6625969973069</v>
       </c>
       <c r="Q21" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R21" t="n">
-        <v>964</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="S21" t="n">
-        <v>790.5826554506689</v>
+        <v>862.8876260635219</v>
       </c>
       <c r="T21" t="n">
-        <v>588.3960608094349</v>
+        <v>660.701031422288</v>
       </c>
       <c r="U21" t="n">
-        <v>588.3960608094349</v>
+        <v>432.4774131586771</v>
       </c>
       <c r="V21" t="n">
-        <v>588.3960608094349</v>
+        <v>197.3253049269343</v>
       </c>
       <c r="W21" t="n">
-        <v>588.3960608094349</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="X21" t="n">
-        <v>588.3960608094349</v>
+        <v>193.7341723913397</v>
       </c>
       <c r="Y21" t="n">
-        <v>588.3960608094349</v>
+        <v>193.7341723913397</v>
       </c>
     </row>
     <row r="22">
@@ -5869,76 +5869,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L22" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M22" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N22" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R22" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U22" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y22" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="23">
@@ -5948,76 +5948,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C23" t="n">
-        <v>720.5656565656566</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="D23" t="n">
-        <v>506.1486868686869</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="E23" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="F23" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="G23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J23" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K23" t="n">
-        <v>122.2389935104989</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L23" t="n">
-        <v>302.3148450951575</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M23" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N23" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O23" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q23" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R23" t="n">
-        <v>964</v>
+        <v>942.6594228129348</v>
       </c>
       <c r="S23" t="n">
-        <v>964</v>
+        <v>731.528039392485</v>
       </c>
       <c r="T23" t="n">
-        <v>964</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="U23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="V23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="W23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="X23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="Y23" t="n">
-        <v>964</v>
+        <v>262.7299197543128</v>
       </c>
     </row>
     <row r="24">
@@ -6027,76 +6027,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>501.9048939478338</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="C24" t="n">
-        <v>327.4518646667068</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="D24" t="n">
-        <v>178.5174550054555</v>
+        <v>668.2068788942177</v>
       </c>
       <c r="E24" t="n">
-        <v>19.28</v>
+        <v>508.9694238887622</v>
       </c>
       <c r="F24" t="n">
-        <v>19.28</v>
+        <v>362.4348659156472</v>
       </c>
       <c r="G24" t="n">
-        <v>19.28</v>
+        <v>223.7040404982626</v>
       </c>
       <c r="H24" t="n">
-        <v>19.28</v>
+        <v>110.334904905842</v>
       </c>
       <c r="I24" t="n">
-        <v>19.28</v>
+        <v>20.03527576299844</v>
       </c>
       <c r="J24" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K24" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L24" t="n">
-        <v>374.6006659261865</v>
+        <v>249.2442489785619</v>
       </c>
       <c r="M24" t="n">
-        <v>374.6006659261865</v>
+        <v>304.2053859195205</v>
       </c>
       <c r="N24" t="n">
-        <v>542.7665223866492</v>
+        <v>542.809531908403</v>
       </c>
       <c r="O24" t="n">
-        <v>781.3565223866492</v>
+        <v>781.4136778972854</v>
       </c>
       <c r="P24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S24" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="U24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="V24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="W24" t="n">
-        <v>964</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="X24" t="n">
-        <v>877.8805297328556</v>
+        <v>761.8705608694022</v>
       </c>
       <c r="Y24" t="n">
-        <v>670.1202309679018</v>
+        <v>761.8705608694022</v>
       </c>
     </row>
     <row r="25">
@@ -6106,76 +6106,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="C25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="D25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="E25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="F25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="G25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K25" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L25" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M25" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N25" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="V25" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="W25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="X25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Y25" t="n">
-        <v>19.28</v>
+        <v>153.8134336004835</v>
       </c>
     </row>
     <row r="26">
@@ -6185,76 +6185,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>262.7143434343434</v>
+        <v>262.7299197543128</v>
       </c>
       <c r="C26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J26" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K26" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L26" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M26" t="n">
-        <v>519.3464847584851</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N26" t="n">
-        <v>725.2010069657244</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O26" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P26" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q26" t="n">
-        <v>964</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R26" t="n">
-        <v>964</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="T26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="U26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="V26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="W26" t="n">
-        <v>964</v>
+        <v>749.627473042513</v>
       </c>
       <c r="X26" t="n">
-        <v>720.5656565656566</v>
+        <v>506.1786963984129</v>
       </c>
       <c r="Y26" t="n">
-        <v>477.1313131313132</v>
+        <v>506.1786963984129</v>
       </c>
     </row>
     <row r="27">
@@ -6264,76 +6264,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>588.024364214978</v>
+        <v>291.8877337080889</v>
       </c>
       <c r="C27" t="n">
-        <v>588.024364214978</v>
+        <v>291.8877337080889</v>
       </c>
       <c r="D27" t="n">
-        <v>439.0899545537268</v>
+        <v>291.8877337080889</v>
       </c>
       <c r="E27" t="n">
-        <v>279.8524995482713</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="F27" t="n">
-        <v>133.3179415751563</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="G27" t="n">
-        <v>19.28</v>
+        <v>132.6502787026334</v>
       </c>
       <c r="H27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J27" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K27" t="n">
-        <v>144.6375600578374</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L27" t="n">
-        <v>374.6006659261865</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="M27" t="n">
-        <v>613.1906659261865</v>
+        <v>257.8852890990952</v>
       </c>
       <c r="N27" t="n">
-        <v>613.1906659261865</v>
+        <v>496.4894350879777</v>
       </c>
       <c r="O27" t="n">
-        <v>711.9619638733197</v>
+        <v>735.0935810768601</v>
       </c>
       <c r="P27" t="n">
-        <v>894.6054414866707</v>
+        <v>917.7370586902109</v>
       </c>
       <c r="Q27" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R27" t="n">
-        <v>964</v>
+        <v>908.2174852541166</v>
       </c>
       <c r="S27" t="n">
-        <v>964</v>
+        <v>734.8001407047855</v>
       </c>
       <c r="T27" t="n">
-        <v>964</v>
+        <v>734.8001407047855</v>
       </c>
       <c r="U27" t="n">
-        <v>964</v>
+        <v>734.8001407047855</v>
       </c>
       <c r="V27" t="n">
-        <v>964</v>
+        <v>499.6480324730428</v>
       </c>
       <c r="W27" t="n">
-        <v>964</v>
+        <v>499.6480324730428</v>
       </c>
       <c r="X27" t="n">
-        <v>964</v>
+        <v>499.6480324730428</v>
       </c>
       <c r="Y27" t="n">
-        <v>756.2397012350461</v>
+        <v>291.8877337080889</v>
       </c>
     </row>
     <row r="28">
@@ -6343,76 +6343,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L28" t="n">
-        <v>46.59412500771298</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M28" t="n">
-        <v>85.78216319993516</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N28" t="n">
-        <v>129.4730138553714</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R28" t="n">
-        <v>153.8122904902707</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="T28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="U28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V28" t="n">
-        <v>153.8122904902707</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y28" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="29">
@@ -6422,76 +6422,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="C29" t="n">
-        <v>953.9083846317729</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="D29" t="n">
-        <v>953.9083846317729</v>
+        <v>348.0024326625565</v>
       </c>
       <c r="E29" t="n">
-        <v>749.5830303030303</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="F29" t="n">
-        <v>506.1486868686869</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="G29" t="n">
-        <v>262.7143434343434</v>
+        <v>104.5536560184564</v>
       </c>
       <c r="H29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J29" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K29" t="n">
-        <v>122.2950059109224</v>
+        <v>122.2961490211351</v>
       </c>
       <c r="L29" t="n">
-        <v>302.3708574955809</v>
+        <v>302.3720006057937</v>
       </c>
       <c r="M29" t="n">
-        <v>519.2904723580616</v>
+        <v>519.3476278686978</v>
       </c>
       <c r="N29" t="n">
-        <v>725.144994565301</v>
+        <v>725.2021500759372</v>
       </c>
       <c r="O29" t="n">
-        <v>874.339944707949</v>
+        <v>874.3971002185853</v>
       </c>
       <c r="P29" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q29" t="n">
-        <v>953.9083846317729</v>
+        <v>953.9655401424092</v>
       </c>
       <c r="R29" t="n">
-        <v>953.9083846317729</v>
+        <v>802.5825927271064</v>
       </c>
       <c r="S29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="T29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="U29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="V29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="W29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="X29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
       <c r="Y29" t="n">
-        <v>953.9083846317729</v>
+        <v>591.4512093066566</v>
       </c>
     </row>
     <row r="30">
@@ -6501,76 +6501,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>419.918063556189</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="C30" t="n">
-        <v>245.465034275062</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="D30" t="n">
-        <v>96.53062461381072</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="E30" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="F30" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="G30" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="H30" t="n">
-        <v>19.28</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="I30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J30" t="n">
-        <v>19.28</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K30" t="n">
-        <v>144.6375600578374</v>
+        <v>144.6387031680501</v>
       </c>
       <c r="L30" t="n">
-        <v>374.6006659261865</v>
+        <v>374.6018090363993</v>
       </c>
       <c r="M30" t="n">
-        <v>613.1906659261865</v>
+        <v>613.2059550252818</v>
       </c>
       <c r="N30" t="n">
-        <v>781.3565223866492</v>
+        <v>851.8101010141643</v>
       </c>
       <c r="O30" t="n">
-        <v>781.3565223866492</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="P30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="Q30" t="n">
-        <v>964</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="R30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="S30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="T30" t="n">
-        <v>862.8304705528857</v>
+        <v>964.0571555106362</v>
       </c>
       <c r="U30" t="n">
-        <v>862.8304705528857</v>
+        <v>735.8335372470253</v>
       </c>
       <c r="V30" t="n">
-        <v>627.6783623211429</v>
+        <v>500.6814290152826</v>
       </c>
       <c r="W30" t="n">
-        <v>627.6783623211429</v>
+        <v>257.2326523711826</v>
       </c>
       <c r="X30" t="n">
-        <v>627.6783623211429</v>
+        <v>49.38115216564972</v>
       </c>
       <c r="Y30" t="n">
-        <v>419.918063556189</v>
+        <v>49.38115216564972</v>
       </c>
     </row>
     <row r="31">
@@ -6580,76 +6580,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="C31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="D31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="E31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="F31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="G31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="H31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="I31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="J31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="K31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="L31" t="n">
-        <v>856.7818345174422</v>
+        <v>46.5952681179257</v>
       </c>
       <c r="M31" t="n">
-        <v>895.9698727096644</v>
+        <v>85.78330631014788</v>
       </c>
       <c r="N31" t="n">
-        <v>939.6607233651007</v>
+        <v>129.4741569655842</v>
       </c>
       <c r="O31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="P31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="Q31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="R31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="S31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="T31" t="n">
-        <v>964</v>
+        <v>153.8134336004835</v>
       </c>
       <c r="U31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="V31" t="n">
-        <v>964</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="W31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="X31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
       <c r="Y31" t="n">
-        <v>829.4677095097293</v>
+        <v>19.28114311021272</v>
       </c>
     </row>
     <row r="32">
@@ -6659,76 +6659,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="C32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="E32" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="F32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J32" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K32" t="n">
-        <v>120.2150059109224</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L32" t="n">
-        <v>300.290857495581</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M32" t="n">
-        <v>504.9505276501126</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N32" t="n">
-        <v>710.8050498573519</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O32" t="n">
-        <v>860</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S32" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T32" t="n">
-        <v>642.8282828282828</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U32" t="n">
-        <v>642.8282828282828</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V32" t="n">
-        <v>451.5434343434343</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="W32" t="n">
-        <v>451.5434343434343</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="X32" t="n">
-        <v>451.5434343434343</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="Y32" t="n">
-        <v>451.5434343434343</v>
+        <v>452.3709090732851</v>
       </c>
     </row>
     <row r="33">
@@ -6738,76 +6738,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="C33" t="n">
-        <v>610.6372480572063</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="D33" t="n">
-        <v>461.702838395955</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="E33" t="n">
-        <v>302.4653833904995</v>
+        <v>109.1649019067709</v>
       </c>
       <c r="F33" t="n">
-        <v>155.9308254173845</v>
+        <v>109.1649019067709</v>
       </c>
       <c r="G33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J33" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K33" t="n">
-        <v>142.5575600578374</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L33" t="n">
-        <v>251.6565223866492</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="M33" t="n">
-        <v>251.6565223866492</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="N33" t="n">
-        <v>464.5065223866492</v>
+        <v>443.7116352270382</v>
       </c>
       <c r="O33" t="n">
-        <v>677.3565223866492</v>
+        <v>656.9516929332361</v>
       </c>
       <c r="P33" t="n">
-        <v>860</v>
+        <v>839.595170546587</v>
       </c>
       <c r="Q33" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R33" t="n">
-        <v>785.0902773383333</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S33" t="n">
-        <v>785.0902773383333</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T33" t="n">
-        <v>785.0902773383333</v>
+        <v>485.9720515415478</v>
       </c>
       <c r="U33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="V33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="W33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="X33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
       <c r="Y33" t="n">
-        <v>785.0902773383333</v>
+        <v>268.4023569122264</v>
       </c>
     </row>
     <row r="34">
@@ -6817,76 +6817,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K34" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L34" t="n">
-        <v>44.51412500771298</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M34" t="n">
-        <v>83.70216319993516</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N34" t="n">
-        <v>127.3930138553715</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O34" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P34" t="n">
-        <v>148.9833604548096</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q34" t="n">
-        <v>61.9509935339062</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y34" t="n">
-        <v>17.2</v>
+        <v>861.5759907321129</v>
       </c>
     </row>
     <row r="35">
@@ -6896,76 +6896,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>234.3717171717172</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="C35" t="n">
-        <v>234.3717171717172</v>
+        <v>452.3709090732851</v>
       </c>
       <c r="D35" t="n">
-        <v>234.3717171717172</v>
+        <v>234.8012144439637</v>
       </c>
       <c r="E35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F35" t="n">
-        <v>234.3717171717172</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J35" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K35" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L35" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M35" t="n">
-        <v>415.2904723580617</v>
+        <v>513.5624350164212</v>
       </c>
       <c r="N35" t="n">
-        <v>621.144994565301</v>
+        <v>719.4169572236606</v>
       </c>
       <c r="O35" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S35" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T35" t="n">
-        <v>642.8282828282828</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U35" t="n">
-        <v>451.5434343434343</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V35" t="n">
-        <v>451.5434343434343</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="W35" t="n">
-        <v>234.3717171717172</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="X35" t="n">
-        <v>234.3717171717172</v>
+        <v>669.9406037026066</v>
       </c>
       <c r="Y35" t="n">
-        <v>234.3717171717172</v>
+        <v>669.9406037026066</v>
       </c>
     </row>
     <row r="36">
@@ -6975,76 +6975,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>483.9331627743991</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="C36" t="n">
-        <v>309.4801334932721</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="D36" t="n">
-        <v>160.5457238320208</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="E36" t="n">
-        <v>160.5457238320208</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="F36" t="n">
-        <v>160.5457238320208</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="G36" t="n">
-        <v>21.81489841463633</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="H36" t="n">
-        <v>21.81489841463633</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I36" t="n">
-        <v>17.95413265278571</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K36" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="L36" t="n">
-        <v>17.2</v>
+        <v>230.4715775208402</v>
       </c>
       <c r="M36" t="n">
-        <v>182.2619638733197</v>
+        <v>435.095875319717</v>
       </c>
       <c r="N36" t="n">
-        <v>395.1119638733197</v>
+        <v>648.335933025915</v>
       </c>
       <c r="O36" t="n">
-        <v>607.9619638733197</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P36" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R36" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S36" t="n">
-        <v>860</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="T36" t="n">
-        <v>860</v>
+        <v>688.1586461827818</v>
       </c>
       <c r="U36" t="n">
-        <v>860</v>
+        <v>470.5889515534603</v>
       </c>
       <c r="V36" t="n">
-        <v>860</v>
+        <v>253.0192569241389</v>
       </c>
       <c r="W36" t="n">
-        <v>860</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="X36" t="n">
-        <v>652.1484997944672</v>
+        <v>35.44956229481744</v>
       </c>
       <c r="Y36" t="n">
-        <v>652.1484997944672</v>
+        <v>35.44956229481744</v>
       </c>
     </row>
     <row r="37">
@@ -7054,76 +7054,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="C37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I37" t="n">
-        <v>747.9621456974897</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J37" t="n">
-        <v>747.9621456974897</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K37" t="n">
-        <v>725.4677095097293</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L37" t="n">
-        <v>752.7818345174422</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M37" t="n">
-        <v>791.9698727096644</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N37" t="n">
-        <v>835.6607233651007</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O37" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P37" t="n">
-        <v>860</v>
+        <v>858.8270606966518</v>
       </c>
       <c r="Q37" t="n">
-        <v>860</v>
+        <v>771.7946937757483</v>
       </c>
       <c r="R37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="S37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="T37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="U37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="V37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="W37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="X37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="Y37" t="n">
-        <v>860</v>
+        <v>727.0437002418422</v>
       </c>
     </row>
     <row r="38">
@@ -7133,76 +7133,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C38" t="n">
-        <v>860</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D38" t="n">
-        <v>642.8282828282828</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E38" t="n">
-        <v>425.6565656565656</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F38" t="n">
-        <v>208.4848484848484</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G38" t="n">
-        <v>208.4848484848484</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H38" t="n">
-        <v>208.4848484848484</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J38" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K38" t="n">
-        <v>22.36462077340309</v>
+        <v>120.2465257255646</v>
       </c>
       <c r="L38" t="n">
-        <v>202.4404723580617</v>
+        <v>300.3223773102232</v>
       </c>
       <c r="M38" t="n">
-        <v>415.2904723580617</v>
+        <v>416.8664630901746</v>
       </c>
       <c r="N38" t="n">
-        <v>621.144994565301</v>
+        <v>622.7209852974139</v>
       </c>
       <c r="O38" t="n">
-        <v>770.339944707949</v>
+        <v>771.915935440062</v>
       </c>
       <c r="P38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T38" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U38" t="n">
-        <v>860</v>
+        <v>644.0062961027915</v>
       </c>
       <c r="V38" t="n">
-        <v>860</v>
+        <v>426.43660147347</v>
       </c>
       <c r="W38" t="n">
-        <v>860</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="X38" t="n">
-        <v>860</v>
+        <v>208.8669068441485</v>
       </c>
       <c r="Y38" t="n">
-        <v>860</v>
+        <v>208.8669068441485</v>
       </c>
     </row>
     <row r="39">
@@ -7212,76 +7212,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>435.0679840633289</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="C39" t="n">
-        <v>325.3718646667068</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="D39" t="n">
-        <v>176.4374550054555</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="E39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="F39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="G39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="H39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="I39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="J39" t="n">
-        <v>17.2</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="K39" t="n">
-        <v>17.2</v>
+        <v>142.5890798724797</v>
       </c>
       <c r="L39" t="n">
-        <v>182.2619638733197</v>
+        <v>355.8291375786776</v>
       </c>
       <c r="M39" t="n">
-        <v>182.2619638733197</v>
+        <v>569.0691952848756</v>
       </c>
       <c r="N39" t="n">
-        <v>395.1119638733197</v>
+        <v>678.932513118762</v>
       </c>
       <c r="O39" t="n">
-        <v>607.9619638733197</v>
+        <v>678.932513118762</v>
       </c>
       <c r="P39" t="n">
-        <v>790.6054414866707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q39" t="n">
-        <v>860</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R39" t="n">
-        <v>860</v>
+        <v>760.4064612849986</v>
       </c>
       <c r="S39" t="n">
-        <v>860</v>
+        <v>586.9891167356675</v>
       </c>
       <c r="T39" t="n">
-        <v>860</v>
+        <v>384.8025220944335</v>
       </c>
       <c r="U39" t="n">
-        <v>642.8282828282828</v>
+        <v>167.2328274651121</v>
       </c>
       <c r="V39" t="n">
-        <v>642.8282828282828</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="W39" t="n">
-        <v>642.8282828282828</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="X39" t="n">
-        <v>642.8282828282828</v>
+        <v>17.23151981464226</v>
       </c>
       <c r="Y39" t="n">
-        <v>435.0679840633289</v>
+        <v>17.23151981464226</v>
       </c>
     </row>
     <row r="40">
@@ -7291,76 +7291,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="C40" t="n">
-        <v>151.7322904902707</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="D40" t="n">
-        <v>151.7322904902707</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="E40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="F40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="G40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="H40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="I40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="J40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="K40" t="n">
-        <v>17.2</v>
+        <v>727.0437002418422</v>
       </c>
       <c r="L40" t="n">
-        <v>44.51412500771298</v>
+        <v>754.3578252495552</v>
       </c>
       <c r="M40" t="n">
-        <v>83.70216319993516</v>
+        <v>793.5458634417773</v>
       </c>
       <c r="N40" t="n">
-        <v>127.3930138553715</v>
+        <v>837.2367140972136</v>
       </c>
       <c r="O40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="P40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Q40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="R40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="S40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="T40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="U40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="V40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="W40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="X40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
       <c r="Y40" t="n">
-        <v>151.7322904902707</v>
+        <v>861.5759907321129</v>
       </c>
     </row>
     <row r="41">
@@ -7370,76 +7370,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>421.6969696969697</v>
+        <v>448.2340696092722</v>
       </c>
       <c r="C41" t="n">
-        <v>206.5454545454546</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="D41" t="n">
-        <v>206.5454545454546</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="E41" t="n">
-        <v>206.5454545454546</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="F41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="G41" t="n">
-        <v>17.04</v>
+        <v>232.6540053493298</v>
       </c>
       <c r="H41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J41" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K41" t="n">
-        <v>17.04</v>
+        <v>107.2817095536563</v>
       </c>
       <c r="L41" t="n">
-        <v>197.1158515846586</v>
+        <v>287.3575611383148</v>
       </c>
       <c r="M41" t="n">
-        <v>407.2904723580617</v>
+        <v>498.6475821194843</v>
       </c>
       <c r="N41" t="n">
-        <v>613.144994565301</v>
+        <v>704.5021043267236</v>
       </c>
       <c r="O41" t="n">
-        <v>762.339944707949</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="P41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="Q41" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R41" t="n">
-        <v>852</v>
+        <v>702.3141070540689</v>
       </c>
       <c r="S41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="T41" t="n">
-        <v>852</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="U41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="V41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="W41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="X41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
       <c r="Y41" t="n">
-        <v>636.8484848484849</v>
+        <v>663.8141338692145</v>
       </c>
     </row>
     <row r="42">
@@ -7449,76 +7449,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>130.4091355924207</v>
+        <v>340.4613800317657</v>
       </c>
       <c r="C42" t="n">
-        <v>130.4091355924207</v>
+        <v>166.0083507506387</v>
       </c>
       <c r="D42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G42" t="n">
-        <v>130.4091355924207</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J42" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K42" t="n">
-        <v>17.04</v>
+        <v>142.4315011472248</v>
       </c>
       <c r="L42" t="n">
-        <v>227.91</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="M42" t="n">
-        <v>360.8654414866706</v>
+        <v>353.7215221283943</v>
       </c>
       <c r="N42" t="n">
-        <v>571.7354414866707</v>
+        <v>565.0115431095638</v>
       </c>
       <c r="O42" t="n">
-        <v>782.6054414866707</v>
+        <v>601.6590183426915</v>
       </c>
       <c r="P42" t="n">
-        <v>782.6054414866707</v>
+        <v>784.3024959560423</v>
       </c>
       <c r="Q42" t="n">
-        <v>852</v>
+        <v>853.6970544693717</v>
       </c>
       <c r="R42" t="n">
-        <v>852</v>
+        <v>771.6215085516504</v>
       </c>
       <c r="S42" t="n">
-        <v>852</v>
+        <v>771.6215085516504</v>
       </c>
       <c r="T42" t="n">
-        <v>852</v>
+        <v>771.6215085516504</v>
       </c>
       <c r="U42" t="n">
-        <v>721.5362865289578</v>
+        <v>556.0414442917081</v>
       </c>
       <c r="V42" t="n">
-        <v>721.5362865289578</v>
+        <v>556.0414442917081</v>
       </c>
       <c r="W42" t="n">
-        <v>506.3847713774426</v>
+        <v>340.4613800317657</v>
       </c>
       <c r="X42" t="n">
-        <v>506.3847713774426</v>
+        <v>340.4613800317657</v>
       </c>
       <c r="Y42" t="n">
-        <v>298.6244726124887</v>
+        <v>340.4613800317657</v>
       </c>
     </row>
     <row r="43">
@@ -7528,76 +7528,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="C43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="D43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="E43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="F43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="G43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="H43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="I43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="J43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="K43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="L43" t="n">
-        <v>44.35412500771298</v>
+        <v>44.38806609710041</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54216319993516</v>
+        <v>83.57610428932259</v>
       </c>
       <c r="N43" t="n">
-        <v>127.2330138553715</v>
+        <v>127.2669549447589</v>
       </c>
       <c r="O43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="P43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="Q43" t="n">
-        <v>151.5722904902707</v>
+        <v>151.6062315796582</v>
       </c>
       <c r="R43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="S43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="T43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="U43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="V43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="W43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="X43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
       <c r="Y43" t="n">
-        <v>17.04</v>
+        <v>17.07394108938743</v>
       </c>
     </row>
     <row r="44">
@@ -8433,19 +8433,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K8" t="n">
-        <v>245.0393459944755</v>
+        <v>244.6749789590202</v>
       </c>
       <c r="L8" t="n">
-        <v>235.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M8" t="n">
-        <v>256.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N8" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O8" t="n">
-        <v>256.0982114216868</v>
+        <v>255.7185026163176</v>
       </c>
       <c r="P8" t="n">
         <v>231.2329957552695</v>
@@ -8512,25 +8512,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K9" t="n">
-        <v>163.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L9" t="n">
-        <v>138.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M9" t="n">
-        <v>142.1340339220183</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N9" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O9" t="n">
-        <v>167.5457393939394</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P9" t="n">
-        <v>159.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q9" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R9" t="n">
         <v>45.52166981132082</v>
@@ -8594,13 +8594,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L10" t="n">
-        <v>160.8846762812385</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M10" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N10" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O10" t="n">
         <v>163.0416663658825</v>
@@ -8670,22 +8670,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K11" t="n">
-        <v>245.0393459944755</v>
+        <v>245.7101422396114</v>
       </c>
       <c r="L11" t="n">
-        <v>235.7664149699872</v>
+        <v>260.3515428840269</v>
       </c>
       <c r="M11" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N11" t="n">
-        <v>255.4130635965909</v>
+        <v>229.4130635965909</v>
       </c>
       <c r="O11" t="n">
-        <v>256.0982114216868</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P11" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q11" t="n">
         <v>212.3149906599047</v>
@@ -8749,13 +8749,13 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K12" t="n">
-        <v>163.841438974359</v>
+        <v>162.4265668883987</v>
       </c>
       <c r="L12" t="n">
-        <v>164.5543797798742</v>
+        <v>164.174670974505</v>
       </c>
       <c r="M12" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N12" t="n">
         <v>131.3417120833333</v>
@@ -8767,7 +8767,7 @@
         <v>133.9744074143302</v>
       </c>
       <c r="Q12" t="n">
-        <v>165.9817740860215</v>
+        <v>165.6020652806523</v>
       </c>
       <c r="R12" t="n">
         <v>45.52166981132082</v>
@@ -8831,13 +8831,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L13" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M13" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N13" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O13" t="n">
         <v>163.0416663658825</v>
@@ -8907,22 +8907,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K14" t="n">
-        <v>246.0898510449805</v>
+        <v>244.6749789590202</v>
       </c>
       <c r="L14" t="n">
-        <v>261.7664149699872</v>
+        <v>261.3867061646181</v>
       </c>
       <c r="M14" t="n">
-        <v>230.3462332272727</v>
+        <v>255.9665244219036</v>
       </c>
       <c r="N14" t="n">
         <v>229.4130635965909</v>
       </c>
       <c r="O14" t="n">
-        <v>255.0477063711817</v>
+        <v>230.0982114216867</v>
       </c>
       <c r="P14" t="n">
-        <v>257.2329957552695</v>
+        <v>256.8532869499004</v>
       </c>
       <c r="Q14" t="n">
         <v>212.3149906599047</v>
@@ -8986,25 +8986,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K15" t="n">
-        <v>163.841438974359</v>
+        <v>163.4617301689898</v>
       </c>
       <c r="L15" t="n">
-        <v>164.5543797798742</v>
+        <v>163.1395076939139</v>
       </c>
       <c r="M15" t="n">
-        <v>167.0835288715133</v>
+        <v>167.7543251166491</v>
       </c>
       <c r="N15" t="n">
         <v>131.3417120833333</v>
       </c>
       <c r="O15" t="n">
-        <v>142.5962444444444</v>
+        <v>168.2165356390753</v>
       </c>
       <c r="P15" t="n">
         <v>133.9744074143302</v>
       </c>
       <c r="Q15" t="n">
-        <v>165.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R15" t="n">
         <v>45.52166981132082</v>
@@ -9068,13 +9068,13 @@
         <v>106.7437663446525</v>
       </c>
       <c r="L16" t="n">
-        <v>160.8846762812383</v>
+        <v>160.5049674758691</v>
       </c>
       <c r="M16" t="n">
-        <v>164.9257839476051</v>
+        <v>164.5460751422359</v>
       </c>
       <c r="N16" t="n">
-        <v>153.6855444652332</v>
+        <v>153.305835659864</v>
       </c>
       <c r="O16" t="n">
         <v>163.0416663658825</v>
@@ -9144,22 +9144,22 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K17" t="n">
-        <v>248.0898510449805</v>
+        <v>220.0898510449805</v>
       </c>
       <c r="L17" t="n">
-        <v>263.7664149699872</v>
+        <v>263.3564402303034</v>
       </c>
       <c r="M17" t="n">
-        <v>257.2149200959596</v>
+        <v>257.9362584875889</v>
       </c>
       <c r="N17" t="n">
-        <v>229.4130635965909</v>
+        <v>257.0030888569071</v>
       </c>
       <c r="O17" t="n">
         <v>230.0982114216867</v>
       </c>
       <c r="P17" t="n">
-        <v>259.2329957552695</v>
+        <v>257.7082725202194</v>
       </c>
       <c r="Q17" t="n">
         <v>212.3149906599047</v>
@@ -9226,22 +9226,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L18" t="n">
-        <v>138.5543797798742</v>
+        <v>166.1444050401903</v>
       </c>
       <c r="M18" t="n">
-        <v>142.1340339220183</v>
+        <v>168.6093106869682</v>
       </c>
       <c r="N18" t="n">
-        <v>158.2103989520202</v>
+        <v>158.9317373436494</v>
       </c>
       <c r="O18" t="n">
-        <v>170.5962444444444</v>
+        <v>170.1862697047606</v>
       </c>
       <c r="P18" t="n">
-        <v>161.9744074143302</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q18" t="n">
-        <v>167.9817740860215</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R18" t="n">
         <v>45.52166981132082</v>
@@ -9308,10 +9308,10 @@
         <v>162.4747015415544</v>
       </c>
       <c r="M19" t="n">
-        <v>166.9257839476051</v>
+        <v>166.5158092079212</v>
       </c>
       <c r="N19" t="n">
-        <v>155.6855444652332</v>
+        <v>155.2755697255493</v>
       </c>
       <c r="O19" t="n">
         <v>163.0416663658825</v>
@@ -9381,7 +9381,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K20" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L20" t="n">
         <v>417.6612145504504</v>
@@ -9460,25 +9460,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K21" t="n">
-        <v>193.3297384877933</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L21" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M21" t="n">
-        <v>383.1340339220183</v>
+        <v>233.2169876979182</v>
       </c>
       <c r="N21" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O21" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P21" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q21" t="n">
-        <v>139.9817740860215</v>
+        <v>210.0772877358491</v>
       </c>
       <c r="R21" t="n">
         <v>45.52166981132082</v>
@@ -9618,7 +9618,7 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K23" t="n">
-        <v>324.0888343889188</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L23" t="n">
         <v>417.6612145504504</v>
@@ -9697,19 +9697,19 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K24" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L24" t="n">
         <v>370.8403453034592</v>
       </c>
       <c r="M24" t="n">
-        <v>142.1340339220183</v>
+        <v>197.6503338623806</v>
       </c>
       <c r="N24" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O24" t="n">
-        <v>383.5962444444444</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P24" t="n">
         <v>318.4627686399372</v>
@@ -9858,7 +9858,7 @@
         <v>324.1454125711647</v>
       </c>
       <c r="L26" t="n">
-        <v>417.6612145504504</v>
+        <v>417.6612145504505</v>
       </c>
       <c r="M26" t="n">
         <v>449.5135334928325</v>
@@ -9867,7 +9867,7 @@
         <v>437.3469244119842</v>
       </c>
       <c r="O26" t="n">
-        <v>380.7436030804994</v>
+        <v>380.8001812627454</v>
       </c>
       <c r="P26" t="n">
         <v>321.7987081714826</v>
@@ -9934,25 +9934,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K27" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L27" t="n">
-        <v>370.8403453034592</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M27" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N27" t="n">
-        <v>131.3417120833333</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O27" t="n">
-        <v>242.3652322698316</v>
+        <v>383.6105333221035</v>
       </c>
       <c r="P27" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q27" t="n">
-        <v>210.0772877358491</v>
+        <v>186.7697506723097</v>
       </c>
       <c r="R27" t="n">
         <v>45.52166981132082</v>
@@ -10098,7 +10098,7 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M29" t="n">
-        <v>449.4569553105865</v>
+        <v>449.5135334928325</v>
       </c>
       <c r="N29" t="n">
         <v>437.3469244119842</v>
@@ -10177,16 +10177,16 @@
         <v>370.8403453034592</v>
       </c>
       <c r="M30" t="n">
-        <v>383.1340339220183</v>
+        <v>383.1483227996774</v>
       </c>
       <c r="N30" t="n">
-        <v>301.2062135585481</v>
+        <v>372.3560009609923</v>
       </c>
       <c r="O30" t="n">
-        <v>142.5962444444444</v>
+        <v>255.9771075721939</v>
       </c>
       <c r="P30" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q30" t="n">
         <v>139.9817740860215</v>
@@ -10335,16 +10335,16 @@
         <v>417.6612145504504</v>
       </c>
       <c r="M32" t="n">
-        <v>437.0731727773048</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N32" t="n">
-        <v>437.3469244119842</v>
+        <v>339.6742254965835</v>
       </c>
       <c r="O32" t="n">
         <v>380.8001812627454</v>
       </c>
       <c r="P32" t="n">
-        <v>231.2329957552695</v>
+        <v>321.7987081714826</v>
       </c>
       <c r="Q32" t="n">
         <v>212.3149906599047</v>
@@ -10408,25 +10408,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K33" t="n">
-        <v>264.4652370125786</v>
+        <v>137.841438974359</v>
       </c>
       <c r="L33" t="n">
-        <v>248.755351829179</v>
+        <v>138.5543797798742</v>
       </c>
       <c r="M33" t="n">
-        <v>142.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N33" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O33" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P33" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q33" t="n">
-        <v>139.9817740860215</v>
+        <v>162.1846227582699</v>
       </c>
       <c r="R33" t="n">
         <v>45.52166981132082</v>
@@ -10566,19 +10566,19 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K35" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L35" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M35" t="n">
-        <v>445.3462332272727</v>
+        <v>445.740230910301</v>
       </c>
       <c r="N35" t="n">
         <v>437.3469244119842</v>
       </c>
       <c r="O35" t="n">
-        <v>380.8001812627454</v>
+        <v>283.1274823473447</v>
       </c>
       <c r="P35" t="n">
         <v>321.7987081714826</v>
@@ -10648,22 +10648,22 @@
         <v>137.841438974359</v>
       </c>
       <c r="L36" t="n">
-        <v>138.5543797798742</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M36" t="n">
-        <v>308.8632903597151</v>
+        <v>348.8252438198737</v>
       </c>
       <c r="N36" t="n">
-        <v>346.3417120833333</v>
+        <v>346.7357097663615</v>
       </c>
       <c r="O36" t="n">
-        <v>357.5962444444444</v>
+        <v>357.9902421274727</v>
       </c>
       <c r="P36" t="n">
-        <v>318.4627686399372</v>
+        <v>133.9744074143302</v>
       </c>
       <c r="Q36" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R36" t="n">
         <v>45.52166981132082</v>
@@ -10803,13 +10803,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K38" t="n">
-        <v>225.3066397049837</v>
+        <v>324.1454125711647</v>
       </c>
       <c r="L38" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M38" t="n">
-        <v>445.3462332272727</v>
+        <v>348.0675319949004</v>
       </c>
       <c r="N38" t="n">
         <v>437.3469244119842</v>
@@ -10882,25 +10882,25 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K39" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L39" t="n">
-        <v>305.2836362175709</v>
+        <v>353.9483774629024</v>
       </c>
       <c r="M39" t="n">
-        <v>142.1340339220183</v>
+        <v>357.5280316050465</v>
       </c>
       <c r="N39" t="n">
-        <v>346.3417120833333</v>
+        <v>242.3147604003903</v>
       </c>
       <c r="O39" t="n">
-        <v>357.5962444444444</v>
+        <v>142.5962444444444</v>
       </c>
       <c r="P39" t="n">
         <v>318.4627686399372</v>
       </c>
       <c r="Q39" t="n">
-        <v>210.0772877358491</v>
+        <v>139.9817740860215</v>
       </c>
       <c r="R39" t="n">
         <v>45.52166981132082</v>
@@ -11040,13 +11040,13 @@
         <v>169.0966151720738</v>
       </c>
       <c r="K41" t="n">
-        <v>220.0898510449805</v>
+        <v>311.2088090896966</v>
       </c>
       <c r="L41" t="n">
         <v>417.6612145504504</v>
       </c>
       <c r="M41" t="n">
-        <v>442.643829968084</v>
+        <v>443.7704968446156</v>
       </c>
       <c r="N41" t="n">
         <v>437.3469244119842</v>
@@ -11055,7 +11055,7 @@
         <v>380.8001812627454</v>
       </c>
       <c r="P41" t="n">
-        <v>321.7987081714826</v>
+        <v>231.2329957552695</v>
       </c>
       <c r="Q41" t="n">
         <v>212.3149906599047</v>
@@ -11119,22 +11119,22 @@
         <v>126.0910353404088</v>
       </c>
       <c r="K42" t="n">
-        <v>137.841438974359</v>
+        <v>264.4652370125786</v>
       </c>
       <c r="L42" t="n">
-        <v>351.5543797798742</v>
+        <v>351.9786433972171</v>
       </c>
       <c r="M42" t="n">
-        <v>276.4324596661301</v>
+        <v>142.1340339220183</v>
       </c>
       <c r="N42" t="n">
-        <v>344.3417120833333</v>
+        <v>344.7659757006762</v>
       </c>
       <c r="O42" t="n">
-        <v>355.5962444444444</v>
+        <v>179.6138961950785</v>
       </c>
       <c r="P42" t="n">
-        <v>133.9744074143302</v>
+        <v>318.4627686399372</v>
       </c>
       <c r="Q42" t="n">
         <v>210.0772877358491</v>
@@ -22981,16 +22981,16 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C8" t="n">
-        <v>342.3720917710075</v>
+        <v>365.2728917710076</v>
       </c>
       <c r="D8" t="n">
-        <v>328.683041620683</v>
+        <v>332.1166891364521</v>
       </c>
       <c r="E8" t="n">
-        <v>355.9303700722618</v>
+        <v>356.3100788776309</v>
       </c>
       <c r="F8" t="n">
-        <v>380.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G8" t="n">
         <v>415.302737515135</v>
@@ -23035,7 +23035,7 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U8" t="n">
-        <v>251.3456529078365</v>
+        <v>225.7253617132057</v>
       </c>
       <c r="V8" t="n">
         <v>327.7522584701349</v>
@@ -23047,7 +23047,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y8" t="n">
-        <v>386.2379386560536</v>
+        <v>360.6176474614227</v>
       </c>
     </row>
     <row r="9">
@@ -23057,13 +23057,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>140.5331836498673</v>
+        <v>143.9668311656365</v>
       </c>
       <c r="C9" t="n">
-        <v>172.7084989883157</v>
+        <v>147.0882077936849</v>
       </c>
       <c r="D9" t="n">
-        <v>147.4450655646388</v>
+        <v>121.8247743700079</v>
       </c>
       <c r="E9" t="n">
         <v>157.6450804554009</v>
@@ -23075,13 +23075,13 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H9" t="n">
-        <v>90.08123556275433</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I9" t="n">
-        <v>63.39663285141508</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -23105,7 +23105,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S9" t="n">
         <v>171.6831711038378</v>
@@ -23120,7 +23120,7 @@
         <v>232.8005871494253</v>
       </c>
       <c r="W9" t="n">
-        <v>251.6949831609196</v>
+        <v>226.0746919662888</v>
       </c>
       <c r="X9" t="n">
         <v>205.7729852034775</v>
@@ -23151,16 +23151,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G10" t="n">
-        <v>167.9909793584588</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H10" t="n">
-        <v>138.6744211998785</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I10" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J10" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -23178,7 +23178,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q10" t="n">
         <v>86.16204325169439</v>
@@ -23260,22 +23260,22 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>149.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S11" t="n">
-        <v>186.1192695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T11" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U11" t="n">
-        <v>225.3456529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V11" t="n">
-        <v>301.7522584701349</v>
+        <v>327.7522584701349</v>
       </c>
       <c r="W11" t="n">
         <v>349.240968717413</v>
@@ -23294,7 +23294,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>166.5331836498673</v>
+        <v>140.9128924552365</v>
       </c>
       <c r="C12" t="n">
         <v>172.7084989883157</v>
@@ -23315,7 +23315,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I12" t="n">
-        <v>89.39663285141508</v>
+        <v>67.5768716934421</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -23345,16 +23345,16 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S12" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T12" t="n">
-        <v>174.1647286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U12" t="n">
-        <v>199.9413820809748</v>
+        <v>225.9413820809748</v>
       </c>
       <c r="V12" t="n">
-        <v>210.6463784756831</v>
+        <v>207.1802959547944</v>
       </c>
       <c r="W12" t="n">
         <v>251.6949831609196</v>
@@ -23363,7 +23363,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y12" t="n">
-        <v>205.6826957773044</v>
+        <v>180.0624045826735</v>
       </c>
     </row>
     <row r="13">
@@ -23388,16 +23388,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G13" t="n">
-        <v>167.9909793584588</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H13" t="n">
-        <v>138.6744211998787</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I13" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J13" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -23415,7 +23415,7 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q13" t="n">
         <v>86.16204325169439</v>
@@ -23497,19 +23497,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>123.8691179411497</v>
+        <v>124.2488267465189</v>
       </c>
       <c r="S14" t="n">
-        <v>183.0200695862453</v>
+        <v>183.3997783916145</v>
       </c>
       <c r="T14" t="n">
-        <v>197.0958495641314</v>
+        <v>197.4755583695005</v>
       </c>
       <c r="U14" t="n">
-        <v>228.4448529078365</v>
+        <v>238.7699996381505</v>
       </c>
       <c r="V14" t="n">
         <v>327.7522584701349</v>
@@ -23543,19 +23543,19 @@
         <v>157.6450804554009</v>
       </c>
       <c r="F15" t="n">
-        <v>145.0692123933839</v>
+        <v>123.2494512354109</v>
       </c>
       <c r="G15" t="n">
-        <v>137.3435171632106</v>
+        <v>111.7232259685798</v>
       </c>
       <c r="H15" t="n">
-        <v>86.23544423649646</v>
+        <v>86.61515304186563</v>
       </c>
       <c r="I15" t="n">
-        <v>89.39663285141508</v>
+        <v>63.77634165678425</v>
       </c>
       <c r="J15" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -23579,13 +23579,13 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>74.15783415264313</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S15" t="n">
-        <v>145.6831711038378</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T15" t="n">
-        <v>177.2639286948216</v>
+        <v>200.1647286948216</v>
       </c>
       <c r="U15" t="n">
         <v>225.9413820809748</v>
@@ -23625,16 +23625,16 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G16" t="n">
-        <v>167.7167873157913</v>
+        <v>167.6941187001108</v>
       </c>
       <c r="H16" t="n">
-        <v>136.2271725074396</v>
+        <v>136.6068813128088</v>
       </c>
       <c r="I16" t="n">
-        <v>129.4504749272583</v>
+        <v>129.8301837326275</v>
       </c>
       <c r="J16" t="n">
-        <v>67.35918011667277</v>
+        <v>67.73888892204195</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -23701,19 +23701,19 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F17" t="n">
-        <v>382.2136457417114</v>
+        <v>394.5240408470375</v>
       </c>
       <c r="G17" t="n">
-        <v>387.302737515135</v>
+        <v>387.7127122548189</v>
       </c>
       <c r="H17" t="n">
-        <v>311.4748021157671</v>
+        <v>311.884776855451</v>
       </c>
       <c r="I17" t="n">
-        <v>182.4758895704059</v>
+        <v>182.8858643100898</v>
       </c>
       <c r="J17" t="n">
-        <v>11.94928935461252</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -23774,13 +23774,13 @@
         <v>172.7084989883157</v>
       </c>
       <c r="D18" t="n">
-        <v>119.4450655646388</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E18" t="n">
-        <v>129.6450804554009</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F18" t="n">
-        <v>120.4068123933839</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G18" t="n">
         <v>137.3435171632106</v>
@@ -23816,16 +23816,16 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>100.1578341526431</v>
+        <v>72.56780889232699</v>
       </c>
       <c r="S18" t="n">
-        <v>171.6831711038378</v>
+        <v>144.0931458435217</v>
       </c>
       <c r="T18" t="n">
-        <v>200.1647286948216</v>
+        <v>172.5747034345055</v>
       </c>
       <c r="U18" t="n">
-        <v>225.9413820809748</v>
+        <v>201.6400878316884</v>
       </c>
       <c r="V18" t="n">
         <v>232.8005871494253</v>
@@ -23837,7 +23837,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y18" t="n">
-        <v>177.6826957773044</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="19">
@@ -23847,7 +23847,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>157.8095125557512</v>
+        <v>179.8319801819373</v>
       </c>
       <c r="C19" t="n">
         <v>167.2468210986278</v>
@@ -23895,25 +23895,25 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R19" t="n">
-        <v>149.2933913771695</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S19" t="n">
-        <v>224.0165980369723</v>
+        <v>201.5678386764629</v>
       </c>
       <c r="T19" t="n">
-        <v>227.9455894282815</v>
+        <v>200.3555641679654</v>
       </c>
       <c r="U19" t="n">
-        <v>286.3190293564909</v>
+        <v>258.7290040961748</v>
       </c>
       <c r="V19" t="n">
-        <v>224.137643323828</v>
+        <v>252.137643323828</v>
       </c>
       <c r="W19" t="n">
-        <v>258.522998336591</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X19" t="n">
-        <v>225.7096553890372</v>
+        <v>198.119630128721</v>
       </c>
       <c r="Y19" t="n">
         <v>218.5846533520948</v>
@@ -23926,22 +23926,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>382.7338416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C20" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D20" t="n">
-        <v>354.683041620683</v>
+        <v>142.3976559772408</v>
       </c>
       <c r="E20" t="n">
         <v>381.9303700722618</v>
       </c>
       <c r="F20" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G20" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H20" t="n">
         <v>339.4748021157671</v>
@@ -23971,7 +23971,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>9.990699214544804</v>
       </c>
       <c r="R20" t="n">
         <v>149.8691179411497</v>
@@ -23980,7 +23980,7 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T20" t="n">
-        <v>20.81374877867617</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U20" t="n">
         <v>251.3456529078365</v>
@@ -23989,13 +23989,13 @@
         <v>327.7522584701349</v>
       </c>
       <c r="W20" t="n">
-        <v>108.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X20" t="n">
         <v>369.731100678469</v>
       </c>
       <c r="Y20" t="n">
-        <v>386.2379386560536</v>
+        <v>145.2236497783945</v>
       </c>
     </row>
     <row r="21">
@@ -24008,19 +24008,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C21" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>24.82456670155162</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H21" t="n">
         <v>112.2354442364965</v>
@@ -24029,7 +24029,7 @@
         <v>89.39663285141508</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -24053,22 +24053,22 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>171.6831711038378</v>
       </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>251.6949831609196</v>
+        <v>248.139761950681</v>
       </c>
       <c r="X21" t="n">
         <v>205.7729852034775</v>
@@ -24135,7 +24135,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S22" t="n">
-        <v>90.82963045160423</v>
+        <v>224.0165980369723</v>
       </c>
       <c r="T22" t="n">
         <v>227.9455894282815</v>
@@ -24144,7 +24144,7 @@
         <v>286.3190293564909</v>
       </c>
       <c r="V22" t="n">
-        <v>252.137643323828</v>
+        <v>118.95067573846</v>
       </c>
       <c r="W22" t="n">
         <v>286.522998336591</v>
@@ -24163,22 +24163,22 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>141.7338416634806</v>
+        <v>382.7338416634806</v>
       </c>
       <c r="C23" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D23" t="n">
-        <v>142.410241620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E23" t="n">
-        <v>140.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F23" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G23" t="n">
-        <v>174.302737515135</v>
+        <v>174.288448637476</v>
       </c>
       <c r="H23" t="n">
         <v>339.4748021157671</v>
@@ -24211,16 +24211,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R23" t="n">
-        <v>149.8691179411497</v>
+        <v>128.6853625704253</v>
       </c>
       <c r="S23" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>223.0958495641314</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>251.3456529078365</v>
+        <v>10.33136403017744</v>
       </c>
       <c r="V23" t="n">
         <v>327.7522584701349</v>
@@ -24242,31 +24242,31 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>54.71802040920606</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>145.0692123933839</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>137.3435171632106</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>89.39663285141508</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7465913262578567</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -24296,7 +24296,7 @@
         <v>171.6831711038378</v>
       </c>
       <c r="T24" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>225.9413820809748</v>
@@ -24308,10 +24308,10 @@
         <v>251.6949831609196</v>
       </c>
       <c r="X24" t="n">
-        <v>120.5147096390045</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="25">
@@ -24336,7 +24336,7 @@
         <v>145.4210480229312</v>
       </c>
       <c r="G25" t="n">
-        <v>167.9909793584588</v>
+        <v>34.80401177309074</v>
       </c>
       <c r="H25" t="n">
         <v>162.2271725074396</v>
@@ -24384,7 +24384,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W25" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X25" t="n">
         <v>225.7096553890372</v>
@@ -24400,10 +24400,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>170.4610416634806</v>
+        <v>141.7195527858215</v>
       </c>
       <c r="C26" t="n">
-        <v>124.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D26" t="n">
         <v>354.683041620683</v>
@@ -24445,13 +24445,13 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>9.990699214544804</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>209.0200695862453</v>
+        <v>156.5945010984978</v>
       </c>
       <c r="T26" t="n">
         <v>223.0958495641314</v>
@@ -24466,10 +24466,10 @@
         <v>349.240968717413</v>
       </c>
       <c r="X26" t="n">
-        <v>128.731100678469</v>
+        <v>128.71681180081</v>
       </c>
       <c r="Y26" t="n">
-        <v>145.2379386560536</v>
+        <v>386.2379386560536</v>
       </c>
     </row>
     <row r="27">
@@ -24479,25 +24479,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C27" t="n">
         <v>172.7084989883157</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G27" t="n">
-        <v>24.44595500380595</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H27" t="n">
-        <v>112.2354442364965</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
         <v>89.39663285141508</v>
@@ -24527,10 +24527,10 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>100.1578341526431</v>
+        <v>44.87656059868869</v>
       </c>
       <c r="S27" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>200.1647286948216</v>
@@ -24539,7 +24539,7 @@
         <v>225.9413820809748</v>
       </c>
       <c r="V27" t="n">
-        <v>232.8005871494253</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>251.6949831609196</v>
@@ -24609,7 +24609,7 @@
         <v>177.2933913771695</v>
       </c>
       <c r="S28" t="n">
-        <v>224.0165980369723</v>
+        <v>90.82963045160423</v>
       </c>
       <c r="T28" t="n">
         <v>227.9455894282815</v>
@@ -24621,7 +24621,7 @@
         <v>252.137643323828</v>
       </c>
       <c r="W28" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X28" t="n">
         <v>225.7096553890372</v>
@@ -24640,22 +24640,22 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C29" t="n">
-        <v>365.2728917710076</v>
+        <v>124.2586028933485</v>
       </c>
       <c r="D29" t="n">
         <v>354.683041620683</v>
       </c>
       <c r="E29" t="n">
-        <v>179.6482692868066</v>
+        <v>140.9160811946027</v>
       </c>
       <c r="F29" t="n">
-        <v>165.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G29" t="n">
-        <v>174.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H29" t="n">
-        <v>98.47480211576715</v>
+        <v>255.0550143366059</v>
       </c>
       <c r="I29" t="n">
         <v>210.4758895704059</v>
@@ -24685,10 +24685,10 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>209.0200695862453</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
         <v>223.0958495641314</v>
@@ -24719,13 +24719,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E30" t="n">
-        <v>81.16696208772834</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F30" t="n">
         <v>145.0692123933839</v>
@@ -24737,7 +24737,7 @@
         <v>112.2354442364965</v>
       </c>
       <c r="I30" t="n">
-        <v>89.39663285141508</v>
+        <v>59.59762388653245</v>
       </c>
       <c r="J30" t="n">
         <v>0.7465913262578567</v>
@@ -24764,7 +24764,7 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S30" t="n">
         <v>171.6831711038378</v>
@@ -24773,19 +24773,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U30" t="n">
-        <v>225.9413820809748</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>251.6949831609196</v>
+        <v>10.68069428326055</v>
       </c>
       <c r="X30" t="n">
-        <v>205.7729852034775</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="31">
@@ -24852,13 +24852,13 @@
         <v>227.9455894282815</v>
       </c>
       <c r="U31" t="n">
-        <v>286.3190293564909</v>
+        <v>153.1320617711229</v>
       </c>
       <c r="V31" t="n">
         <v>252.137643323828</v>
       </c>
       <c r="W31" t="n">
-        <v>153.336030751223</v>
+        <v>286.522998336591</v>
       </c>
       <c r="X31" t="n">
         <v>225.7096553890372</v>
@@ -24883,10 +24883,10 @@
         <v>354.683041620683</v>
       </c>
       <c r="E32" t="n">
-        <v>166.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F32" t="n">
-        <v>191.8760457417114</v>
+        <v>191.4820480586832</v>
       </c>
       <c r="G32" t="n">
         <v>415.302737515135</v>
@@ -24928,13 +24928,13 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T32" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U32" t="n">
         <v>251.3456529078365</v>
       </c>
       <c r="V32" t="n">
-        <v>138.3802584701349</v>
+        <v>112.3582607871067</v>
       </c>
       <c r="W32" t="n">
         <v>349.240968717413</v>
@@ -24943,7 +24943,7 @@
         <v>369.731100678469</v>
       </c>
       <c r="Y32" t="n">
-        <v>386.2379386560536</v>
+        <v>196.5189054968423</v>
       </c>
     </row>
     <row r="33">
@@ -24956,19 +24956,19 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>145.0692123933839</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>46.32946889200326</v>
       </c>
       <c r="H33" t="n">
         <v>112.2354442364965</v>
@@ -25001,16 +25001,16 @@
         <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>25.9972087175931</v>
+        <v>100.1578341526431</v>
       </c>
       <c r="S33" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V33" t="n">
         <v>232.8005871494253</v>
@@ -25032,7 +25032,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179.8319801819373</v>
+        <v>46.6450125965693</v>
       </c>
       <c r="C34" t="n">
         <v>167.2468210986278</v>
@@ -25074,13 +25074,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.721440735106512</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>86.16204325169439</v>
       </c>
       <c r="R34" t="n">
-        <v>132.9899077786023</v>
+        <v>177.2933913771695</v>
       </c>
       <c r="S34" t="n">
         <v>224.0165980369723</v>
@@ -25114,19 +25114,19 @@
         <v>382.7338416634806</v>
       </c>
       <c r="C35" t="n">
-        <v>365.2728917710076</v>
+        <v>149.8788940879793</v>
       </c>
       <c r="D35" t="n">
-        <v>354.683041620683</v>
+        <v>139.2890439376547</v>
       </c>
       <c r="E35" t="n">
-        <v>381.9303700722618</v>
+        <v>166.5363723892335</v>
       </c>
       <c r="F35" t="n">
         <v>406.8760457417114</v>
       </c>
       <c r="G35" t="n">
-        <v>200.302737515135</v>
+        <v>415.302737515135</v>
       </c>
       <c r="H35" t="n">
         <v>339.4748021157671</v>
@@ -25165,16 +25165,16 @@
         <v>209.0200695862453</v>
       </c>
       <c r="T35" t="n">
-        <v>8.095849564131356</v>
+        <v>223.0958495641314</v>
       </c>
       <c r="U35" t="n">
-        <v>61.97365290783654</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V35" t="n">
-        <v>327.7522584701349</v>
+        <v>138.0332253109237</v>
       </c>
       <c r="W35" t="n">
-        <v>134.240968717413</v>
+        <v>349.240968717413</v>
       </c>
       <c r="X35" t="n">
         <v>369.731100678469</v>
@@ -25190,13 +25190,13 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E36" t="n">
         <v>157.6450804554009</v>
@@ -25205,16 +25205,16 @@
         <v>145.0692123933839</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>137.3435171632106</v>
       </c>
       <c r="H36" t="n">
-        <v>112.2354442364965</v>
+        <v>94.19958218112303</v>
       </c>
       <c r="I36" t="n">
-        <v>85.57447474718296</v>
+        <v>89.39663285141508</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>0.7465913262578567</v>
       </c>
       <c r="K36" t="n">
         <v>0</v>
@@ -25241,22 +25241,22 @@
         <v>100.1578341526431</v>
       </c>
       <c r="S36" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
         <v>200.1647286948216</v>
       </c>
       <c r="U36" t="n">
-        <v>225.9413820809748</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V36" t="n">
-        <v>232.8005871494253</v>
+        <v>17.40658946639704</v>
       </c>
       <c r="W36" t="n">
-        <v>251.6949831609196</v>
+        <v>36.30098547789137</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>205.7729852034775</v>
       </c>
       <c r="Y36" t="n">
         <v>205.6826957773044</v>
@@ -25290,13 +25290,13 @@
         <v>162.2271725074396</v>
       </c>
       <c r="I37" t="n">
-        <v>44.53299916777313</v>
+        <v>155.4504749272583</v>
       </c>
       <c r="J37" t="n">
         <v>93.35918011667277</v>
       </c>
       <c r="K37" t="n">
-        <v>0</v>
+        <v>22.26949182588285</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -25311,13 +25311,13 @@
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2.721440735106512</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>86.16204325169439</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>177.2933913771695</v>
+        <v>132.9899077786024</v>
       </c>
       <c r="S37" t="n">
         <v>224.0165980369723</v>
@@ -25348,19 +25348,19 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>382.7338416634806</v>
+        <v>193.0148085042694</v>
       </c>
       <c r="C38" t="n">
         <v>365.2728917710076</v>
       </c>
       <c r="D38" t="n">
-        <v>139.683041620683</v>
+        <v>354.683041620683</v>
       </c>
       <c r="E38" t="n">
-        <v>166.9303700722618</v>
+        <v>381.9303700722618</v>
       </c>
       <c r="F38" t="n">
-        <v>191.8760457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G38" t="n">
         <v>415.302737515135</v>
@@ -25369,7 +25369,7 @@
         <v>339.4748021157671</v>
       </c>
       <c r="I38" t="n">
-        <v>21.10388957040598</v>
+        <v>210.4758895704059</v>
       </c>
       <c r="J38" t="n">
         <v>11.94928935461252</v>
@@ -25405,13 +25405,13 @@
         <v>223.0958495641314</v>
       </c>
       <c r="U38" t="n">
-        <v>251.3456529078365</v>
+        <v>35.95165522480826</v>
       </c>
       <c r="V38" t="n">
-        <v>327.7522584701349</v>
+        <v>112.3582607871067</v>
       </c>
       <c r="W38" t="n">
-        <v>349.240968717413</v>
+        <v>133.8469710343848</v>
       </c>
       <c r="X38" t="n">
         <v>369.731100678469</v>
@@ -25430,13 +25430,13 @@
         <v>166.5331836498673</v>
       </c>
       <c r="C39" t="n">
-        <v>64.10934078565984</v>
+        <v>172.7084989883157</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>147.4450655646388</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>157.6450804554009</v>
       </c>
       <c r="F39" t="n">
         <v>145.0692123933839</v>
@@ -25475,19 +25475,19 @@
         <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>100.1578341526431</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>171.6831711038378</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>200.1647286948216</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>10.94138208097482</v>
+        <v>10.54738439794659</v>
       </c>
       <c r="V39" t="n">
-        <v>232.8005871494253</v>
+        <v>84.29929257546016</v>
       </c>
       <c r="W39" t="n">
         <v>251.6949831609196</v>
@@ -25496,7 +25496,7 @@
         <v>205.7729852034775</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="40">
@@ -25509,13 +25509,13 @@
         <v>179.8319801819373</v>
       </c>
       <c r="C40" t="n">
-        <v>167.2468210986278</v>
+        <v>34.05985351325984</v>
       </c>
       <c r="D40" t="n">
         <v>148.6154730182124</v>
       </c>
       <c r="E40" t="n">
-        <v>13.24699506120112</v>
+        <v>146.4339626465692</v>
       </c>
       <c r="F40" t="n">
         <v>145.4210480229312</v>
@@ -25585,10 +25585,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>169.7338416634806</v>
+        <v>169.3095780461377</v>
       </c>
       <c r="C41" t="n">
-        <v>152.2728917710076</v>
+        <v>151.8486281536646</v>
       </c>
       <c r="D41" t="n">
         <v>354.683041620683</v>
@@ -25597,13 +25597,13 @@
         <v>381.9303700722618</v>
       </c>
       <c r="F41" t="n">
-        <v>219.2656457417114</v>
+        <v>406.8760457417114</v>
       </c>
       <c r="G41" t="n">
         <v>415.302737515135</v>
       </c>
       <c r="H41" t="n">
-        <v>339.4748021157671</v>
+        <v>126.0505384984242</v>
       </c>
       <c r="I41" t="n">
         <v>210.4758895704059</v>
@@ -25633,16 +25633,16 @@
         <v>9.990699214544804</v>
       </c>
       <c r="R41" t="n">
-        <v>149.8691179411497</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>209.0200695862453</v>
+        <v>170.9050961332395</v>
       </c>
       <c r="T41" t="n">
         <v>223.0958495641314</v>
       </c>
       <c r="U41" t="n">
-        <v>38.3456529078365</v>
+        <v>251.3456529078365</v>
       </c>
       <c r="V41" t="n">
         <v>327.7522584701349</v>
@@ -25664,13 +25664,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>166.5331836498673</v>
       </c>
       <c r="C42" t="n">
-        <v>172.7084989883157</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>147.4450655646388</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>157.6450804554009</v>
@@ -25682,7 +25682,7 @@
         <v>137.3435171632106</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>112.2354442364965</v>
       </c>
       <c r="I42" t="n">
         <v>89.39663285141508</v>
@@ -25712,7 +25712,7 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>100.1578341526431</v>
+        <v>18.90304369409913</v>
       </c>
       <c r="S42" t="n">
         <v>171.6831711038378</v>
@@ -25721,19 +25721,19 @@
         <v>200.1647286948216</v>
       </c>
       <c r="U42" t="n">
-        <v>96.78230574464305</v>
+        <v>12.5171184636319</v>
       </c>
       <c r="V42" t="n">
         <v>232.8005871494253</v>
       </c>
       <c r="W42" t="n">
-        <v>38.69498316091961</v>
+        <v>38.27071954357669</v>
       </c>
       <c r="X42" t="n">
         <v>205.7729852034775</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>205.6826957773044</v>
       </c>
     </row>
     <row r="43">
@@ -25791,7 +25791,7 @@
         <v>86.16204325169439</v>
       </c>
       <c r="R43" t="n">
-        <v>44.10642379180143</v>
+        <v>44.10642379180146</v>
       </c>
       <c r="S43" t="n">
         <v>224.0165980369723</v>
@@ -26094,7 +26094,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>350350.0795405007</v>
+        <v>350035.0587549795</v>
       </c>
     </row>
     <row r="5">
@@ -26102,7 +26102,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="6">
@@ -26110,7 +26110,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>350350.0795405005</v>
+        <v>350035.0587549793</v>
       </c>
     </row>
     <row r="7">
@@ -26118,7 +26118,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>351994.6487060302</v>
+        <v>351669.2246312143</v>
       </c>
     </row>
     <row r="8">
@@ -26126,7 +26126,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="9">
@@ -26134,7 +26134,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>506779.7343245365</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="10">
@@ -26142,7 +26142,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="11">
@@ -26150,7 +26150,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>506779.7343245363</v>
+        <v>506790.0512205641</v>
       </c>
     </row>
     <row r="12">
@@ -26158,7 +26158,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="13">
@@ -26166,7 +26166,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105898</v>
       </c>
     </row>
     <row r="14">
@@ -26174,7 +26174,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>488007.1404845364</v>
+        <v>488291.6158105897</v>
       </c>
     </row>
     <row r="15">
@@ -26182,7 +26182,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>486563.0948045364</v>
+        <v>486869.422826439</v>
       </c>
     </row>
     <row r="16">
@@ -26261,49 +26261,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="C2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
       <c r="D2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="E2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548872</v>
       </c>
       <c r="F2" t="n">
-        <v>51690.99534204105</v>
+        <v>51644.51686548873</v>
       </c>
       <c r="G2" t="n">
-        <v>51933.63669433229</v>
+        <v>51885.62330624471</v>
       </c>
       <c r="H2" t="n">
-        <v>74770.78047411186</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="I2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909959</v>
       </c>
       <c r="J2" t="n">
-        <v>74770.78047411187</v>
+        <v>74772.30263909958</v>
       </c>
       <c r="K2" t="n">
-        <v>74770.78047411185</v>
+        <v>74772.30263909957</v>
       </c>
       <c r="L2" t="n">
-        <v>72001.05351411185</v>
+        <v>72043.0252835296</v>
       </c>
       <c r="M2" t="n">
-        <v>72001.05351411187</v>
+        <v>72043.02528352961</v>
       </c>
       <c r="N2" t="n">
-        <v>72001.05351411187</v>
+        <v>72043.02528352961</v>
       </c>
       <c r="O2" t="n">
-        <v>71787.99759411189</v>
+        <v>71833.1935317696</v>
       </c>
       <c r="P2" t="n">
-        <v>48378.33248915087</v>
+        <v>48378.33248915088</v>
       </c>
     </row>
     <row r="3">
@@ -26319,7 +26319,7 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8076.38</v>
+        <v>7958.431053788175</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -26328,10 +26328,10 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>548.1700000000001</v>
+        <v>539.8745613933579</v>
       </c>
       <c r="H3" t="n">
-        <v>57469.317</v>
+        <v>57583.78714233168</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -26365,49 +26365,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>262.4692517857578</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>262.4692517857578</v>
       </c>
       <c r="D4" t="n">
-        <v>22.53282218066301</v>
+        <v>302.7659019667079</v>
       </c>
       <c r="E4" t="n">
-        <v>22.532822180663</v>
+        <v>302.7659019667079</v>
       </c>
       <c r="F4" t="n">
-        <v>22.532822180663</v>
+        <v>302.7659019667079</v>
       </c>
       <c r="G4" t="n">
-        <v>24.1832752112465</v>
+        <v>305.7405600937579</v>
       </c>
       <c r="H4" t="n">
-        <v>179.5221438966159</v>
+        <v>588.1056701472498</v>
       </c>
       <c r="I4" t="n">
-        <v>179.5221438966159</v>
+        <v>588.1056701472498</v>
       </c>
       <c r="J4" t="n">
-        <v>179.5221438966159</v>
+        <v>588.1056701472498</v>
       </c>
       <c r="K4" t="n">
-        <v>179.5221438966159</v>
+        <v>588.1056701472498</v>
       </c>
       <c r="L4" t="n">
-        <v>160.6823863208583</v>
+        <v>554.43312684536</v>
       </c>
       <c r="M4" t="n">
-        <v>160.6823863208583</v>
+        <v>554.43312684536</v>
       </c>
       <c r="N4" t="n">
-        <v>160.6823863208583</v>
+        <v>554.43312684536</v>
       </c>
       <c r="O4" t="n">
-        <v>159.2331741996462</v>
+        <v>551.8443211555209</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>262.4692517857578</v>
       </c>
     </row>
     <row r="5">
@@ -26423,40 +26423,40 @@
         <v>33627.6</v>
       </c>
       <c r="D5" t="n">
-        <v>35208.4</v>
+        <v>35185.31370463355</v>
       </c>
       <c r="E5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="F5" t="n">
-        <v>1580.8</v>
+        <v>1557.713704633554</v>
       </c>
       <c r="G5" t="n">
-        <v>1702.4</v>
+        <v>1677.473535827221</v>
       </c>
       <c r="H5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="I5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="J5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="K5" t="n">
-        <v>14652.8</v>
+        <v>14653.66876376167</v>
       </c>
       <c r="L5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="M5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="N5" t="n">
-        <v>13072</v>
+        <v>13095.95505912812</v>
       </c>
       <c r="O5" t="n">
-        <v>12950.4</v>
+        <v>12976.19522793445</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -26469,49 +26469,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14750.73248915088</v>
+        <v>14488.26323736513</v>
       </c>
       <c r="C6" t="n">
-        <v>14750.73248915087</v>
+        <v>14488.26323736513</v>
       </c>
       <c r="D6" t="n">
-        <v>8383.682519860391</v>
+        <v>8198.00620510029</v>
       </c>
       <c r="E6" t="n">
-        <v>50087.66251986038</v>
+        <v>49784.03725888846</v>
       </c>
       <c r="F6" t="n">
-        <v>50087.66251986038</v>
+        <v>49784.03725888847</v>
       </c>
       <c r="G6" t="n">
-        <v>49658.88341912105</v>
+        <v>49362.53464893037</v>
       </c>
       <c r="H6" t="n">
-        <v>2469.141330215243</v>
+        <v>1946.741062858964</v>
       </c>
       <c r="I6" t="n">
-        <v>59938.45833021526</v>
+        <v>59530.52820519067</v>
       </c>
       <c r="J6" t="n">
-        <v>59938.45833021526</v>
+        <v>59530.52820519065</v>
       </c>
       <c r="K6" t="n">
-        <v>59938.45833021523</v>
+        <v>59530.52820519064</v>
       </c>
       <c r="L6" t="n">
-        <v>58768.37112779099</v>
+        <v>58392.63709755613</v>
       </c>
       <c r="M6" t="n">
-        <v>58768.37112779102</v>
+        <v>58392.63709755614</v>
       </c>
       <c r="N6" t="n">
-        <v>58768.37112779102</v>
+        <v>58392.63709755614</v>
       </c>
       <c r="O6" t="n">
-        <v>58678.36441991224</v>
+        <v>58305.15398267963</v>
       </c>
       <c r="P6" t="n">
-        <v>48378.33248915087</v>
+        <v>48115.86323736513</v>
       </c>
     </row>
   </sheetData>
@@ -26733,40 +26733,40 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="G4" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="H4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="I4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="J4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="K4" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="L4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N4" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -26840,49 +26840,49 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -26892,49 +26892,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -26950,19 +26950,19 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="E4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="H4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -26971,22 +26971,22 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -27191,7 +27191,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -27200,10 +27200,10 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>2</v>
+        <v>1.969734065685309</v>
       </c>
       <c r="P4" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
     </row>
   </sheetData>
@@ -35088,19 +35088,19 @@
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>24.94949494949496</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N8" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35167,25 +35167,25 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>24.94949494949496</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -35249,13 +35249,13 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>26.00000000000018</v>
+        <v>25.62029119463084</v>
       </c>
       <c r="M10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N10" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O10" t="n">
         <v>24.58512791403967</v>
@@ -35325,22 +35325,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>24.94949494949496</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -35404,13 +35404,13 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M12" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -35422,7 +35422,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35486,13 +35486,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N13" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O13" t="n">
         <v>24.58512791403967</v>
@@ -35562,22 +35562,22 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="L14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>24.94949494949495</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35641,25 +35641,25 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="L15" t="n">
-        <v>26</v>
+        <v>24.58512791403969</v>
       </c>
       <c r="M15" t="n">
-        <v>24.94949494949495</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35723,13 +35723,13 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="M16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="N16" t="n">
-        <v>26</v>
+        <v>25.62029119463083</v>
       </c>
       <c r="O16" t="n">
         <v>24.58512791403967</v>
@@ -35799,22 +35799,22 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M17" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>28</v>
+        <v>26.47527676494983</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -35881,22 +35881,22 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>26.47527676494984</v>
       </c>
       <c r="N18" t="n">
-        <v>26.86868686868687</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O18" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="P18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -35963,10 +35963,10 @@
         <v>27.59002526031614</v>
       </c>
       <c r="M19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="N19" t="n">
-        <v>28</v>
+        <v>27.59002526031614</v>
       </c>
       <c r="O19" t="n">
         <v>24.58512791403967</v>
@@ -36036,7 +36036,7 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L20" t="n">
         <v>181.8947995804632</v>
@@ -36045,7 +36045,7 @@
         <v>219.1673002655598</v>
       </c>
       <c r="N20" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O20" t="n">
         <v>150.7019698410586</v>
@@ -36115,25 +36115,25 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>55.48829951343433</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L21" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>241</v>
+        <v>91.0829537758999</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O21" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P21" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>70.09551364982758</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36273,7 +36273,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>103.9989833439383</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L23" t="n">
         <v>181.8947995804632</v>
@@ -36352,19 +36352,19 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
         <v>232.285965523585</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>55.51629994036225</v>
       </c>
       <c r="N24" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O24" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P24" t="n">
         <v>184.4883612256069</v>
@@ -36522,7 +36522,7 @@
         <v>207.9338608153932</v>
       </c>
       <c r="O26" t="n">
-        <v>150.6453916588127</v>
+        <v>150.7019698410586</v>
       </c>
       <c r="P26" t="n">
         <v>90.5657124162131</v>
@@ -36589,25 +36589,25 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>232.285965523585</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O27" t="n">
-        <v>99.7689878253871</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="P27" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q27" t="n">
-        <v>70.09551364982758</v>
+        <v>46.78797658628819</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -36753,10 +36753,10 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M29" t="n">
-        <v>219.1107220833138</v>
+        <v>219.1673002655598</v>
       </c>
       <c r="N29" t="n">
-        <v>207.9338608153932</v>
+        <v>207.9338608153933</v>
       </c>
       <c r="O29" t="n">
         <v>150.7019698410586</v>
@@ -36832,16 +36832,16 @@
         <v>232.285965523585</v>
       </c>
       <c r="M30" t="n">
-        <v>241</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="N30" t="n">
-        <v>169.8645014752148</v>
+        <v>241.0142888776591</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>113.3808631277494</v>
       </c>
       <c r="P30" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -36990,16 +36990,16 @@
         <v>181.8947995804632</v>
       </c>
       <c r="M32" t="n">
-        <v>206.726939550032</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N32" t="n">
-        <v>207.9338608153932</v>
+        <v>110.2611618999926</v>
       </c>
       <c r="O32" t="n">
         <v>150.7019698410586</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>90.5657124162131</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -37063,25 +37063,25 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>126.6237980382196</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>110.2009720493048</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O33" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P33" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>22.20284867224837</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37221,19 +37221,19 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L35" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M35" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N35" t="n">
         <v>207.9338608153932</v>
       </c>
       <c r="O35" t="n">
-        <v>150.7019698410586</v>
+        <v>53.02927092565796</v>
       </c>
       <c r="P35" t="n">
         <v>90.5657124162131</v>
@@ -37303,22 +37303,22 @@
         <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M36" t="n">
-        <v>166.7292564376967</v>
+        <v>206.6912098978554</v>
       </c>
       <c r="N36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="O36" t="n">
-        <v>215</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="P36" t="n">
-        <v>184.4883612256069</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37458,13 +37458,13 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>5.216788660003122</v>
+        <v>104.0555615261842</v>
       </c>
       <c r="L38" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M38" t="n">
-        <v>215</v>
+        <v>117.7212987676277</v>
       </c>
       <c r="N38" t="n">
         <v>207.9338608153932</v>
@@ -37537,25 +37537,25 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L39" t="n">
-        <v>166.7292564376967</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>215.3939976830282</v>
       </c>
       <c r="N39" t="n">
-        <v>215</v>
+        <v>110.973048317057</v>
       </c>
       <c r="O39" t="n">
-        <v>215</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>184.4883612256069</v>
       </c>
       <c r="Q39" t="n">
-        <v>70.09551364982758</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37695,13 +37695,13 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>91.118958044716</v>
       </c>
       <c r="L41" t="n">
         <v>181.8947995804632</v>
       </c>
       <c r="M41" t="n">
-        <v>212.2975967408112</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="N41" t="n">
         <v>207.9338608153932</v>
@@ -37710,7 +37710,7 @@
         <v>150.7019698410586</v>
       </c>
       <c r="P41" t="n">
-        <v>90.5657124162131</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -37774,22 +37774,22 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0</v>
+        <v>126.6237980382196</v>
       </c>
       <c r="L42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="M42" t="n">
-        <v>134.2984257441118</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>213</v>
+        <v>213.4242636173429</v>
       </c>
       <c r="O42" t="n">
-        <v>213</v>
+        <v>37.01765175063403</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>184.4883612256069</v>
       </c>
       <c r="Q42" t="n">
         <v>70.09551364982758</v>
